--- a/fhir/StructureDefinition-ehealth-relatedperson.xlsx
+++ b/fhir/StructureDefinition-ehealth-relatedperson.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="409">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -349,7 +349,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -582,7 +582,7 @@
     <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -647,7 +647,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>required</t>
+    <t>extensible</t>
   </si>
   <si>
     <t>http://ehealth.sundhed.dk/vs/relatedperson-relationshiptype</t>
@@ -727,10 +727,378 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension('http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-telecom-purpose').value.ofType(Coding).code}
+</t>
+  </si>
+  <si>
     <t>telecom</t>
   </si>
   <si>
     <t>NK1-5 / NK1-6 / NK1-40</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms</t>
+  </si>
+  <si>
+    <t>video-appointment-reminder-sms</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose</t>
+  </si>
+  <si>
+    <t>purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-telecom-purpose}
+</t>
+  </si>
+  <si>
+    <t>Purpose of telecom contact point</t>
+  </si>
+  <si>
+    <t>The purpose of a telecom contact point on a RelatedPerson.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.url</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-telecom-purpose</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.value[x]</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/vs/telecom-purpose</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.value[x].id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.value[x].extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.value[x].system</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.value[x].system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.value[x].version</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.value[x].version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.value[x].code</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.value[x].code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.value[x].display</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.value[x].display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.extension:purpose.value[x].userSelected</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.extension.value[x].userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.system</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.system</t>
+  </si>
+  <si>
+    <t>phone | fax | email | pager | url | sms | other</t>
+  </si>
+  <si>
+    <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
+  </si>
+  <si>
+    <t>sms</t>
+  </si>
+  <si>
+    <t>Telecommunications form for contact point.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
+  </si>
+  <si>
+    <t>ContactPoint.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpt-2
+</t>
+  </si>
+  <si>
+    <t>./scheme</t>
+  </si>
+  <si>
+    <t>XTN.3</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.value</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.value</t>
+  </si>
+  <si>
+    <t>The actual contact point details</t>
+  </si>
+  <si>
+    <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
+  </si>
+  <si>
+    <t>Additional text data such as phone extension numbers, or notes about use of the contact are sometimes included in the value.</t>
+  </si>
+  <si>
+    <t>Need to support legacy numbers that are not in a tightly controlled format.</t>
+  </si>
+  <si>
+    <t>ContactPoint.value</t>
+  </si>
+  <si>
+    <t>./url</t>
+  </si>
+  <si>
+    <t>XTN.1 (or XTN.12)</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.use</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.use</t>
+  </si>
+  <si>
+    <t>home | work | temp | old | mobile - purpose of this contact point</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for the contact point.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
+  </si>
+  <si>
+    <t>Use of contact point.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
+  </si>
+  <si>
+    <t>ContactPoint.use</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>XTN.2 - but often indicated by field</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.rank</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positiveInt
+</t>
+  </si>
+  <si>
+    <t>Specify preferred order of use (1 = highest)</t>
+  </si>
+  <si>
+    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
+  </si>
+  <si>
+    <t>Note that rank does not necessarily follow the order in which the contacts are represented in the instance.</t>
+  </si>
+  <si>
+    <t>ContactPoint.rank</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom:video-appointment-reminder-sms.period</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when the contact point was/is in use</t>
+  </si>
+  <si>
+    <t>Time period when the contact point was/is in use.</t>
+  </si>
+  <si>
+    <t>ContactPoint.period</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
   </si>
   <si>
     <t>RelatedPerson.gender</t>
@@ -818,10 +1186,6 @@
   </si>
   <si>
     <t>RelatedPerson.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>Period of time that this relationship is considered valid</t>
@@ -1212,12 +1576,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM33"/>
+  <dimension ref="A1:AM53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="78.87109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.99609375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="27.328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1240,9 +1604,9 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="58.23828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.47265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="97.58203125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -3669,16 +4033,14 @@
         <v>74</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>222</v>
@@ -3696,23 +4058,25 @@
         <v>95</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
@@ -3733,17 +4097,19 @@
         <v>84</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>103</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>74</v>
@@ -3768,13 +4134,13 @@
         <v>74</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>234</v>
+        <v>74</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>235</v>
+        <v>74</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>74</v>
@@ -3792,13 +4158,13 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
@@ -3807,21 +4173,21 @@
         <v>95</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3841,16 +4207,16 @@
         <v>74</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>187</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3901,7 +4267,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3913,10 +4279,10 @@
         <v>74</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>74</v>
@@ -3927,10 +4293,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3938,7 +4304,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>76</v>
@@ -3950,21 +4316,19 @@
         <v>74</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>129</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
+        <v>130</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>74</v>
       </c>
@@ -4000,19 +4364,19 @@
         <v>74</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>195</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4024,35 +4388,37 @@
         <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>248</v>
+        <v>74</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -4064,18 +4430,16 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>74</v>
       </c>
@@ -4123,7 +4487,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4135,24 +4499,24 @@
         <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>74</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>256</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4175,13 +4539,13 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>187</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
+        <v>188</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4232,7 +4596,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>189</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4244,13 +4608,13 @@
         <v>74</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>261</v>
+        <v>190</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>74</v>
@@ -4258,10 +4622,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4272,7 +4636,7 @@
         <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -4284,20 +4648,16 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>128</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>129</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>74</v>
       </c>
@@ -4333,19 +4693,19 @@
         <v>74</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4357,10 +4717,10 @@
         <v>74</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>74</v>
@@ -4371,10 +4731,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4382,7 +4742,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>83</v>
@@ -4397,22 +4757,24 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>74</v>
@@ -4454,10 +4816,10 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>83</v>
@@ -4469,7 +4831,7 @@
         <v>74</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>190</v>
+        <v>126</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>74</v>
@@ -4480,21 +4842,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>74</v>
@@ -4506,17 +4868,15 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>74</v>
@@ -4541,13 +4901,11 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>74</v>
+        <v>258</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4565,22 +4923,22 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>195</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>190</v>
+        <v>126</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>74</v>
@@ -4591,46 +4949,42 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>273</v>
+        <v>74</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>128</v>
+        <v>186</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>274</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>74</v>
       </c>
@@ -4678,22 +5032,22 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>189</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>74</v>
@@ -4704,21 +5058,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>74</v>
@@ -4730,20 +5084,18 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>192</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>74</v>
       </c>
@@ -4767,46 +5119,46 @@
         <v>74</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>195</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>74</v>
@@ -4817,10 +5169,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4840,22 +5192,22 @@
         <v>74</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>74</v>
@@ -4904,7 +5256,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -4919,12 +5271,2236 @@
         <v>95</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-relatedperson.xlsx
+++ b/fhir/StructureDefinition-ehealth-relatedperson.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-relatedperson.xlsx
+++ b/fhir/StructureDefinition-ehealth-relatedperson.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-relatedperson.xlsx
+++ b/fhir/StructureDefinition-ehealth-relatedperson.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-relatedperson.xlsx
+++ b/fhir/StructureDefinition-ehealth-relatedperson.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-relatedperson.xlsx
+++ b/fhir/StructureDefinition-ehealth-relatedperson.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-relatedperson.xlsx
+++ b/fhir/StructureDefinition-ehealth-relatedperson.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
